--- a/case_studies/test/carriers_list.xlsx
+++ b/case_studies/test/carriers_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D75986-6091-4443-8303-BFA765CB6375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C32BF6-A25A-4F96-87CC-FC402DA377F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>electricity</t>
   </si>
@@ -37,6 +37,36 @@
   </si>
   <si>
     <t>CARRIERS</t>
+  </si>
+  <si>
+    <t>syngas</t>
+  </si>
+  <si>
+    <t>methane</t>
+  </si>
+  <si>
+    <t>feedgas</t>
+  </si>
+  <si>
+    <t>methanol</t>
+  </si>
+  <si>
+    <t>methane_bio</t>
+  </si>
+  <si>
+    <t>crackergas</t>
+  </si>
+  <si>
+    <t>olefins</t>
+  </si>
+  <si>
+    <t>heat</t>
+  </si>
+  <si>
+    <t>CO2captured</t>
+  </si>
+  <si>
+    <t>naphtha</t>
   </si>
 </sst>
 </file>
@@ -363,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -386,6 +416,56 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/case_studies/test/carriers_list.xlsx
+++ b/case_studies/test/carriers_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C32BF6-A25A-4F96-87CC-FC402DA377F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35D3846-CC76-41E4-BC92-EB254D630AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>electricity</t>
   </si>
@@ -39,34 +39,13 @@
     <t>CARRIERS</t>
   </si>
   <si>
-    <t>syngas</t>
-  </si>
-  <si>
-    <t>methane</t>
-  </si>
-  <si>
-    <t>feedgas</t>
-  </si>
-  <si>
-    <t>methanol</t>
-  </si>
-  <si>
-    <t>methane_bio</t>
-  </si>
-  <si>
-    <t>crackergas</t>
-  </si>
-  <si>
     <t>olefins</t>
   </si>
   <si>
-    <t>heat</t>
+    <t>naphtha</t>
   </si>
   <si>
     <t>CO2captured</t>
-  </si>
-  <si>
-    <t>naphtha</t>
   </si>
 </sst>
 </file>
@@ -393,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -431,41 +410,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
